--- a/Assets/Art/sound/sounddata.xlsx
+++ b/Assets/Art/sound/sounddata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MINSH\Desktop\g1\Assets\Art\sound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04E419EE-5F2C-4976-B25D-4053A3359EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59502989-BA6B-4F1E-A2DB-E43809E750B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9750" yWindow="3570" windowWidth="21600" windowHeight="11295" xr2:uid="{06EF3A75-D1AA-4A81-868A-BB8B132B9953}"/>
+    <workbookView xWindow="3060" yWindow="930" windowWidth="21600" windowHeight="11295" xr2:uid="{06EF3A75-D1AA-4A81-868A-BB8B132B9953}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>鑰匙從鞋子掉出的音效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>點擊教師桌子抽屜鎖上的聲音</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,11 +145,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>克為打開紙條後看向鬼魂驚嚇聲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鬼魂驚嚇亂跑的風聲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sobbing.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\sobbing.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\</t>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\bookTurning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bookTurning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>克維打開紙條後看向鬼魂驚嚇聲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rollbook.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\rollbook.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑰匙從鞋子掉落至地板的音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keydropping.wav</t>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\keydropping.wav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,23 +585,35 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
       <c r="C3" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
       <c r="C4" t="s">
         <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -581,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -595,15 +641,21 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
       <c r="C7" t="s">
         <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -613,13 +665,22 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -627,7 +688,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -635,13 +699,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -649,13 +713,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -663,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
         <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -677,7 +741,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -685,7 +752,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -693,7 +763,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -704,5 +777,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Art/sound/sounddata.xlsx
+++ b/Assets/Art/sound/sounddata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MINSH\Desktop\g1\Assets\Art\sound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59502989-BA6B-4F1E-A2DB-E43809E750B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A69550D-25C7-4F48-9386-C3E1F787800F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="930" windowWidth="21600" windowHeight="11295" xr2:uid="{06EF3A75-D1AA-4A81-868A-BB8B132B9953}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,9 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>\Assets\Art\sound\</t>
-  </si>
-  <si>
     <t>\Assets\Art\sound\bookTurning.wav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,6 +185,55 @@
   </si>
   <si>
     <t>\Assets\Art\sound\keydropping.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clickwood.wav</t>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\clickwood.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clicklock.wav</t>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\clicklock.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paperturning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\paperturning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shocking.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\shocking.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windrunning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\windrunning.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>footsteps.mp3</t>
+  </si>
+  <si>
+    <t>\Assets\Art\sound\footsteps.mp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走路聲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -607,13 +653,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -649,24 +695,27 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -674,24 +723,27 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -740,38 +792,56 @@
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
       <c r="C16" t="s">
         <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
